--- a/AssesmentRACircuitos.xlsx
+++ b/AssesmentRACircuitos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cresu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E4873B-0EE6-4A73-BC40-B04BD4936B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47224D8B-833F-4D05-A11A-56B460B08139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4E9231FD-D7D4-4DB9-827C-7BBB8C2AB79E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4E9231FD-D7D4-4DB9-827C-7BBB8C2AB79E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -463,12 +463,6 @@
     <t>RA1. Definir la arquitectura de un sistema inteligente (Visión Artificial o Edge AI) para la identificación y diagnóstico autónomo de fallas en equipos electrónicos industriales.                                   RA2. Programar Algoritmos de Aprendizaje Automático (Machine Learning/Deep Learning) para su despliegue eficiente en plataformas embebidas con recursos limitados.                                                      RA3. Mantener la operación de los sistemas electrónicos inteligentes, emitiendo un diagnóstico predictivo de fallas en tiempo real a partir del análisis de las señales.</t>
   </si>
   <si>
-    <t>RA1:Analizar el comportamiento matemático de señales y sistemas en tiempo discreto (Qué) para el procesamiento digital de información (Para qué) utilizando ecuaciones en diferencias, convolución discreta y la Transformada Z (Cómo).                                                                                                                              RA2:Validar los procesos de conversión Analógico-Digital y Digital-Analógico (Qué) para garantizar la fidelidad de la señal y evitar el fenómeno de aliasing (Para qué) aplicando el teorema de muestreo de Nyquist y técnicas de reconstrucción ideal y práctica (Cómo).                                                                       RA3:Elaborar algoritmos básicos de procesamiento en el dominio del tiempo (Qué) para realizar operaciones de filtrado y correlación en secuencias de datos (Para qué) mediante el desarrollo de software de simulación matemática o scripts de programación (Cómo).</t>
-  </si>
-  <si>
-    <t>RA1:Diseñar filtros digitales con respuesta al impulso finita (FIR) e infinita (IIR) (Qué) para eñ acondicionamiento de señales y la eliminación de componentes frecuenciales no deseados (Para qué) utilizando métodos de enventanado y algoritmos de optimización espectral (Cómo).                                                                                                                                                         RA2:Aplicar técnicas de análisis espectral y transformada rápida de Fourier (FFT) (Qué) para la caracterización del contenido frecuencial de señales de telecomunicaciones en tiempo real (Para qué) empleando hardware de procesamiento digital (DSP/FPGA) o software de ingeniería (Cómo).                                                                                                                                                                                                        RA3:Integrar algoritmos de procesamiento digital avanzado en sistemas de comunicación (Qué) para la compensación de distorsiones del canal y mejorar la recepción (Para qué) implementando ecualizadores, bancos de filtros y técnicas multitasa en entornos de Radio Definido por Software (SDR) (Cómo).</t>
-  </si>
-  <si>
     <t>Ondas planas, polarización, reflexión y la refracción</t>
   </si>
   <si>
@@ -485,27 +479,6 @@
   </si>
   <si>
     <t>Redes LAN, AN. modelo OSI, la arquitectura TCP/IP, direccionamiento IPv4/IPv6, enrutamiento y conmutación. Protocolos de aplicación, seguridad en redes y servicios web</t>
-  </si>
-  <si>
-    <t>RA1:Analizar los fenómenos de propagación de ondas planas y las ecuaciones de Maxwell (Qué) para predecirla predicción del comportamiento de los campos en diferentes medios de transmisión (Para qué) mediante la resolución matemática y la simulación computacional de escenarios electromagnéticos (Cómo).                                                                                                                                                                                                                RA2: Caracterizar los parámetros de reflexión, refracción y polarización de la onda (Qué) para determinar la viabilidad teórica de un enlace de radiofrecuencia (Para qué) a través del cálculo de coeficientes y el modelado de fronteras entre medios dieléctricos (Cómo).                                                                                RA3:Evaluar la distribución e intensidad de los campos eléctricos y magnéticos en el entorno (Qué) para el cumplimiento de normativas de seguridad y compatibilidad electromagnética (Para qué) utilizando instrumentos de medición de campo y comparando con los límites de exposición permitidos (Cómo).</t>
-  </si>
-  <si>
-    <t>RA1:Diseñar sistemas de transmisión guiados (cobre/fibra) y no guiados (Qué) para garantizar la transferencia eficiente decorriente e información (Para qué) calculando enlaces de potencia, atenuación y adaptación de impedancias en la línea (Cómo).                                                                                                           RA2: Seleccionar antenas y sistemas radiantes  (Qué) para el calculo de la cobertura y directividad en un sistema de telecomunicaciones (Para qué) basándose en la interpretación de patrones de radiación, ganancia y especificaciones técnicas de fabricantes (Cómo).                                                                                                   RA3:Diagnosticar el estado físico y operativo de enlaces de fibra óptica y cableado estructurado (Qué) para el mantenimiento de la continuidad del servicio de red (Para qué) empleando instrumentación especializada como OTDR, certificadores de cableado y analizadores de espectro (Cómo).</t>
-  </si>
-  <si>
-    <t>RA1:Modelar señales determinísticas y aleatorias en los dominios del tiempo y la frecuencia (Qué) para el análisis de sistemas de transmisión analógicos (Para qué) aplicando la Transformada de Fourier, la convolución y teoremas de muestreo (Cómo).                                                                                                        RA2:Elaborar circuitos y algoritmos de modulación y demodulación analógica (AM/FM) (Qué) para la transmisión de señales de voz y audio (Para qué) utilizando arquitecturas de receptores superheterodinos simulados y con prototipos de laboratorio (Cómo).                                                                                RA3:Analizar el impacto del ruido  y las interferencias en el canal de comunicación (Qué) para determinar la fidelidad de la señal recuperada (Para qué) mediante el cálculo y medición de la relación señal a ruido (SNR) y la figura de ruido del sistema (Cómo).</t>
-  </si>
-  <si>
-    <t>RA1:Desarrollar arquitecturas  de Internet de las Cosas (Qué) para la adquisición y gestión de datos en entornos industriales o urbanos (Para qué) integrando sensores, microcontroladores y servicios en la nube mediante protocolos eficientes como MQTT o CoAP (Cómo).                                                                                                                                                                                     RA2:Construir redes de comunicación de bajo consumo y largo alcance (Qué) para la conexión de dispositivos remotos con autonomía energética (Para qué) configurando nodos y gateways sobre tecnologías LPWAN (LoRaWAN/Sigfox) y programación en C/C++ (Cómo).                                                              RA3:Asegurar el ecosistema de dispositivos conectados y el flujo de datos (Qué) para protección de la infraestructura contra vulnerabilidades y accesos no autorizados (Para qué) aplicando cifrado TLS/SSL, gestión de certificados y autenticación robusta desde el borde (Cómo).</t>
-  </si>
-  <si>
-    <t>RA1:Planificar el uso eficiente del espectro radioeléctrico y la topología de red (Qué) para la predicción de viabilidad de cobertura y capacidad de servicios móviles y fijos (Para qué) aplicando la normativa vigente (ANE/CRC) y modelos de propagación para frecuencias de microondas y milimétricas (Cómo).                                                                                                                                                                              RA2:Dimensionar enlaces de telecomunicaciones terrestres y satelitales (Qué) para el establecimiento de conectividad en diferentes escenarios geográficos (Para qué) calculando y considerando parámetros de microondas y de órbitas (GEO/LEO) y tecnologías de acceso (Cómo).                                                                                                                                                                                                RA3:Analizar las tecnologías emergentes en comunicaciones móviles como 5G y 6G (Qué) para la formulación de soluciones de conectividad masiva e inteligente (Para qué) evaluando técnicas de Beamforming, Massive MIMO y gestión dinámica del espectro (Cómo).</t>
-  </si>
-  <si>
-    <t>RA1:Diseñar arquitecturas de red escalables, seguras y convergentes (Qué) para el  soporte de  la demanda de servicios de datos y aplicaciones (Para qué) aplicando los modelos de referencia OSI/TCP-IP y esquemas de direccionamiento IPv4/IPv6 (VLSM) (Cómo).                                                                    RA2:Configurar la infraestructura de enrutamiento y conmutación (Qué) para la distribución del flujo de tráfico y la segmentación lógica de la red (Para qué) implementando protocolos dinámicos (OSPF/BGP), VLANs y políticas de Calidad de Servicio (QoS) (Cómo).                                                                                              RA3:Implementar estrategias de seguridad perimetral y acceso remoto (Qué) para la protección de los activos de información y garantizar la disponibilidad del servicio (Para qué) desplegando Listas de Control de Acceso (ACL), túneles VPN y sistemas de detección de intrusos (Cómo).</t>
-  </si>
-  <si>
-    <t>RA1:Analizar el comportamiento matemático de señales y sistemas en tiempo discreto (Qué) para el procesamiento digital de información (Para qué) utilizando ecuaciones en diferencias, convolución discreta y la Transformada Z (Cómo).                                                                                                                              RA2:Validar los procesos de conversión Analógico-Digital y Digital-Analógico (Qué) para garantizar la fidelidad de la señal y evitar el fenómeno de aliasing (Para qué) aplicando el teorema de muestreo de Nyquist y técnicas de reconstrucción ideal y práctica (Cómo).                                                                       RA3:Implementar algoritmos básicos de procesamiento en el dominio del tiempo (Qué) para realizar operaciones de filtrado y correlación en secuencias de datos (Para qué) mediante el desarrollo de software de simulación matemática o scripts de programación (Cómo).</t>
   </si>
   <si>
     <t>Espacio Académico</t>
@@ -649,9 +622,6 @@
     <t>Formulación y evaluación de proyectos</t>
   </si>
   <si>
-    <t>RA1 (Concebir): Analizar un problema definiendo una arquitectura de sistema ciberfísico, seleccionando los actuadores y sensores justificando su interconexión mediante la integración hardware/software.                                                                                                                                                                                               RA2. (Diseñar): Modelar un sistema mecatrónico, aplicando principios de diseño sistémico y cumpliendo con las especificaciones de cinemática y dinámica.                                                                                                                                           RA3. (Implementar/Operar): Integrar de hardware y software en un entorno de simulación o experimental, validando la arquitectura propuesta y la capacidad de respuesta y del sistema.</t>
-  </si>
-  <si>
     <t>RA1. (Concebir): Definir  los requerimientos funcionales y las viabilidades (técnica, social, ambiental) de un proyecto mecatrónico de complejidad inicial, aplicando metodologías ágiles (SCRUM) para la planificación y el pensamiento sistémico.                                                                                                                                                                                                  RA2.  (Diseñar): Desarrollar la solución integral de un sistema o producto mecatrónico (primer nivel), generando la documentación técnica requerida (normas ISO) y estableciendo el proceso de integración hardware/software del proyecto.                                                                                                                                                                                                  RA3. (Implementar/Operar): Construir el prototipo funcional del proyecto, demostrando su operación bajo condiciones de prueba y documentando los resultados de validación.</t>
   </si>
   <si>
@@ -774,6 +744,36 @@
   </si>
   <si>
     <t>Tecnología en Robotíca y Automatización Industrial</t>
+  </si>
+  <si>
+    <t>RA1.Analizar el comportamiento matemático de señales y sistemas en tiempo discreto (Qué) para el procesamiento digital de información (Para qué) utilizando ecuaciones en diferencias, convolución discreta y la Transformada Z (Cómo).                                                                                                                              RA2.Validar los procesos de conversión Analógico-Digital y Digital-Analógico (Qué) para garantizar la fidelidad de la señal y evitar el fenómeno de aliasing (Para qué) aplicando el teorema de muestreo de Nyquist y técnicas de reconstrucción ideal y práctica (Cómo).                                                                       RA3.Elaborar algoritmos básicos de procesamiento en el dominio del tiempo (Qué) para realizar operaciones de filtrado y correlación en secuencias de datos (Para qué) mediante el desarrollo de software de simulación matemática o scripts de programación (Cómo).</t>
+  </si>
+  <si>
+    <t>RA1.Diseñar filtros digitales con respuesta al impulso finita (FIR) e infinita (IIR) (Qué) para eñ acondicionamiento de señales y la eliminación de componentes frecuenciales no deseados (Para qué) utilizando métodos de enventanado y algoritmos de optimización espectral (Cómo).                                                                                                                                                         RA2.Aplicar técnicas de análisis espectral y transformada rápida de Fourier (FFT) (Qué) para la caracterización del contenido frecuencial de señales de telecomunicaciones en tiempo real (Para qué) empleando hardware de procesamiento digital (DSP/FPGA) o software de ingeniería (Cómo).                                                                                                                                                                                                        RA3.Integrar algoritmos de procesamiento digital avanzado en sistemas de comunicación (Qué) para la compensación de distorsiones del canal y mejorar la recepción (Para qué) implementando ecualizadores, bancos de filtros y técnicas multitasa en entornos de Radio Definido por Software (SDR) (Cómo).</t>
+  </si>
+  <si>
+    <t>RA1.Analizar los fenómenos de propagación de ondas planas y las ecuaciones de Maxwell (Qué) para predecirla predicción del comportamiento de los campos en diferentes medios de transmisión (Para qué) mediante la resolución matemática y la simulación computacional de escenarios electromagnéticos (Cómo).                                                                                                                                                                                                                RA2. Caracterizar los parámetros de reflexión, refracción y polarización de la onda (Qué) para determinar la viabilidad teórica de un enlace de radiofrecuencia (Para qué) a través del cálculo de coeficientes y el modelado de fronteras entre medios dieléctricos (Cómo).                                                                                RA3.Evaluar la distribución e intensidad de los campos eléctricos y magnéticos en el entorno (Qué) para el cumplimiento de normativas de seguridad y compatibilidad electromagnética (Para qué) utilizando instrumentos de medición de campo y comparando con los límites de exposición permitidos (Cómo).</t>
+  </si>
+  <si>
+    <t>RA1.Diseñar sistemas de transmisión guiados (cobre/fibra) y no guiados (Qué) para garantizar la transferencia eficiente decorriente e información (Para qué) calculando enlaces de potencia, atenuación y adaptación de impedancias en la línea (Cómo).                                                                                                           RA2. Seleccionar antenas y sistemas radiantes  (Qué) para el calculo de la cobertura y directividad en un sistema de telecomunicaciones (Para qué) basándose en la interpretación de patrones de radiación, ganancia y especificaciones técnicas de fabricantes (Cómo).                                                                                                   RA3.Diagnosticar el estado físico y operativo de enlaces de fibra óptica y cableado estructurado (Qué) para el mantenimiento de la continuidad del servicio de red (Para qué) empleando instrumentación especializada como OTDR, certificadores de cableado y analizadores de espectro (Cómo).</t>
+  </si>
+  <si>
+    <t>RA1.Modelar señales determinísticas y aleatorias en los dominios del tiempo y la frecuencia (Qué) para el análisis de sistemas de transmisión analógicos (Para qué) aplicando la Transformada de Fourier, la convolución y teoremas de muestreo (Cómo).                                                                                                        RA2.Elaborar circuitos y algoritmos de modulación y demodulación analógica (AM/FM) (Qué) para la transmisión de señales de voz y audio (Para qué) utilizando arquitecturas de receptores superheterodinos simulados y con prototipos de laboratorio (Cómo).                                                                                RA3.Analizar el impacto del ruido  y las interferencias en el canal de comunicación (Qué) para determinar la fidelidad de la señal recuperada (Para qué) mediante el cálculo y medición de la relación señal a ruido (SNR) y la figura de ruido del sistema (Cómo).</t>
+  </si>
+  <si>
+    <t>RA1.Desarrollar arquitecturas  de Internet de las Cosas (Qué) para la adquisición y gestión de datos en entornos industriales o urbanos (Para qué) integrando sensores, microcontroladores y servicios en la nube mediante protocolos eficientes como MQTT o CoAP (Cómo).                                                                                                                                                                                     RA2.Construir redes de comunicación de bajo consumo y largo alcance (Qué) para la conexión de dispositivos remotos con autonomía energética (Para qué) configurando nodos y gateways sobre tecnologías LPWAN (LoRaWAN/Sigfox) y programación en C/C++ (Cómo).                                                              RA3.Asegurar el ecosistema de dispositivos conectados y el flujo de datos (Qué) para protección de la infraestructura contra vulnerabilidades y accesos no autorizados (Para qué) aplicando cifrado TLS/SSL, gestión de certificados y autenticación robusta desde el borde (Cómo).</t>
+  </si>
+  <si>
+    <t>RA1.Planificar el uso eficiente del espectro radioeléctrico y la topología de red (Qué) para la predicción de viabilidad de cobertura y capacidad de servicios móviles y fijos (Para qué) aplicando la normativa vigente (ANE/CRC) y modelos de propagación para frecuencias de microondas y milimétricas (Cómo).                                                                                                                                                                              RA2.Dimensionar enlaces de telecomunicaciones terrestres y satelitales (Qué) para el establecimiento de conectividad en diferentes escenarios geográficos (Para qué) calculando y considerando parámetros de microondas y de órbitas (GEO/LEO) y tecnologías de acceso (Cómo).                                                                                                                                                                                                RA3.Analizar las tecnologías emergentes en comunicaciones móviles como 5G y 6G (Qué) para la formulación de soluciones de conectividad masiva e inteligente (Para qué) evaluando técnicas de Beamforming, Massive MIMO y gestión dinámica del espectro (Cómo).</t>
+  </si>
+  <si>
+    <t>RA1.Diseñar arquitecturas de red escalables, seguras y convergentes (Qué) para el  soporte de  la demanda de servicios de datos y aplicaciones (Para qué) aplicando los modelos de referencia OSI/TCP-IP y esquemas de direccionamiento IPv4/IPv6 (VLSM) (Cómo).                                                                    RA2.Configurar la infraestructura de enrutamiento y conmutación (Qué) para la distribución del flujo de tráfico y la segmentación lógica de la red (Para qué) implementando protocolos dinámicos (OSPF/BGP), VLANs y políticas de Calidad de Servicio (QoS) (Cómo).                                                                                              RA3.Implementar estrategias de seguridad perimetral y acceso remoto (Qué) para la protección de los activos de información y garantizar la disponibilidad del servicio (Para qué) desplegando Listas de Control de Acceso (ACL), túneles VPN y sistemas de detección de intrusos (Cómo).</t>
+  </si>
+  <si>
+    <t>RA1.Analizar el comportamiento matemático de señales y sistemas en tiempo discreto (Qué) para el procesamiento digital de información (Para qué) utilizando ecuaciones en diferencias, convolución discreta y la Transformada Z (Cómo).                                                                                                                              RA2.Validar los procesos de conversión Analógico-Digital y Digital-Analógico (Qué) para garantizar la fidelidad de la señal y evitar el fenómeno de aliasing (Para qué) aplicando el teorema de muestreo de Nyquist y técnicas de reconstrucción ideal y práctica (Cómo).                                                                       RA3.Implementar algoritmos básicos de procesamiento en el dominio del tiempo (Qué) para realizar operaciones de filtrado y correlación en secuencias de datos (Para qué) mediante el desarrollo de software de simulación matemática o scripts de programación (Cómo).</t>
+  </si>
+  <si>
+    <t>RA1. (Concebir): Analizar un problema definiendo una arquitectura de sistema ciberfísico, seleccionando los actuadores y sensores justificando su interconexión mediante la integración hardware/software.                                                                                                                                                                                               RA2. (Diseñar): Modelar un sistema mecatrónico, aplicando principios de diseño sistémico y cumpliendo con las especificaciones de cinemática y dinámica.                                                                                                                                           RA3. (Implementar/Operar): Integrar de hardware y software en un entorno de simulación o experimental, validando la arquitectura propuesta y la capacidad de respuesta y del sistema.</t>
   </si>
 </sst>
 </file>
@@ -1299,15 +1299,15 @@
   <sheetData>
     <row r="1" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B1" s="21" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E1" s="21"/>
       <c r="F1" s="14" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="G1" s="16">
         <v>2026</v>
@@ -1315,15 +1315,15 @@
     </row>
     <row r="2" spans="2:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="21" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C2" s="21"/>
       <c r="D2" s="19" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E2" s="19"/>
       <c r="F2" s="14" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="G2" s="16">
         <v>1</v>
@@ -1340,7 +1340,7 @@
         <v>34</v>
       </c>
       <c r="C4" t="str">
-        <v xml:space="preserve">1:Desarrollar arquitecturas  de Internet de las Cosas (Qué) para la adquisición y gestión de datos en entornos industriales o urbanos (Para qué) integrando sensores, microcontroladores y servicios en la nube mediante protocolos eficientes como MQTT o CoAP (Cómo).                                                                                                                                                                                     </v>
+        <v xml:space="preserve">1.Analizar los fenómenos de propagación de ondas planas y las ecuaciones de Maxwell (Qué) para predecirla predicción del comportamiento de los campos en diferentes medios de transmisión (Para qué) mediante la resolución matemática y la simulación computacional de escenarios electromagnéticos (Cómo).                                                                                                                                                                                                                </v>
       </c>
       <c r="O4" s="18" t="s">
         <v>44</v>
@@ -1355,7 +1355,7 @@
         <v>35</v>
       </c>
       <c r="C5" t="str">
-        <v xml:space="preserve">2:Construir redes de comunicación de bajo consumo y largo alcance (Qué) para la conexión de dispositivos remotos con autonomía energética (Para qué) configurando nodos y gateways sobre tecnologías LPWAN (LoRaWAN/Sigfox) y programación en C/C++ (Cómo).                                                              </v>
+        <v xml:space="preserve">2. Caracterizar los parámetros de reflexión, refracción y polarización de la onda (Qué) para determinar la viabilidad teórica de un enlace de radiofrecuencia (Para qué) a través del cálculo de coeficientes y el modelado de fronteras entre medios dieléctricos (Cómo).                                                                                </v>
       </c>
       <c r="O5" s="18"/>
       <c r="P5" s="18"/>
@@ -1368,7 +1368,7 @@
         <v>36</v>
       </c>
       <c r="C6" t="str">
-        <v>3:Asegurar el ecosistema de dispositivos conectados y el flujo de datos (Qué) para protección de la infraestructura contra vulnerabilidades y accesos no autorizados (Para qué) aplicando cifrado TLS/SSL, gestión de certificados y autenticación robusta desde el borde (Cómo).</v>
+        <v>3.Evaluar la distribución e intensidad de los campos eléctricos y magnéticos en el entorno (Qué) para el cumplimiento de normativas de seguridad y compatibilidad electromagnética (Para qué) utilizando instrumentos de medición de campo y comparando con los límites de exposición permitidos (Cómo).</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>5</v>
@@ -1396,21 +1396,21 @@
       </c>
       <c r="E7" s="3" t="str">
         <f>_xlfn.CONCAT(B4,C4)</f>
-        <v xml:space="preserve">RA1:1:Desarrollar arquitecturas  de Internet de las Cosas (Qué) para la adquisición y gestión de datos en entornos industriales o urbanos (Para qué) integrando sensores, microcontroladores y servicios en la nube mediante protocolos eficientes como MQTT o CoAP (Cómo).                                                                                                                                                                                     </v>
+        <v xml:space="preserve">RA1:1.Analizar los fenómenos de propagación de ondas planas y las ecuaciones de Maxwell (Qué) para predecirla predicción del comportamiento de los campos en diferentes medios de transmisión (Para qué) mediante la resolución matemática y la simulación computacional de escenarios electromagnéticos (Cómo).                                                                                                                                                                                                                </v>
       </c>
       <c r="F7" s="9" t="s">
         <v>3</v>
       </c>
       <c r="G7" s="3" t="str">
         <f>_xlfn.CONCAT(B5,C5)</f>
-        <v xml:space="preserve">RA2:2:Construir redes de comunicación de bajo consumo y largo alcance (Qué) para la conexión de dispositivos remotos con autonomía energética (Para qué) configurando nodos y gateways sobre tecnologías LPWAN (LoRaWAN/Sigfox) y programación en C/C++ (Cómo).                                                              </v>
+        <v xml:space="preserve">RA2:2. Caracterizar los parámetros de reflexión, refracción y polarización de la onda (Qué) para determinar la viabilidad teórica de un enlace de radiofrecuencia (Para qué) a través del cálculo de coeficientes y el modelado de fronteras entre medios dieléctricos (Cómo).                                                                                </v>
       </c>
       <c r="H7" s="9" t="s">
         <v>2</v>
       </c>
       <c r="I7" s="3" t="str">
         <f>_xlfn.CONCAT(B6,C6)</f>
-        <v>RA3:3:Asegurar el ecosistema de dispositivos conectados y el flujo de datos (Qué) para protección de la infraestructura contra vulnerabilidades y accesos no autorizados (Para qué) aplicando cifrado TLS/SSL, gestión de certificados y autenticación robusta desde el borde (Cómo).</v>
+        <v>RA3:3.Evaluar la distribución e intensidad de los campos eléctricos y magnéticos en el entorno (Qué) para el cumplimiento de normativas de seguridad y compatibilidad electromagnética (Para qué) utilizando instrumentos de medición de campo y comparando con los límites de exposición permitidos (Cómo).</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>15</v>
@@ -1465,7 +1465,7 @@
         <v>Deficiente: No logra identificar los conceptos fundamentales ni aplicar los procedimientos básicos requeridos para el análisis y resolución de los problemas planteados.Presenta dificultades para ejecutar actividades de laboratorio y simulación, incluso con acompañamiento docente, lo que evidencia una ausencia de apropiación conceptual y procedimental.</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>25</v>
@@ -1514,7 +1514,7 @@
         <v>Deficiente: No logra identificar los conceptos fundamentales ni aplicar los procedimientos básicos requeridos para el análisis y resolución de los problemas planteados.Presenta dificultades para ejecutar actividades de laboratorio y simulación, incluso con acompañamiento docente, lo que evidencia una ausencia de apropiación conceptual y procedimental.</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>38</v>
@@ -1864,13 +1864,13 @@
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>45</v>
@@ -1887,13 +1887,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
@@ -1907,13 +1907,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
@@ -1927,13 +1927,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
         <v>52</v>
@@ -1947,13 +1947,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
         <v>54</v>
@@ -1967,13 +1967,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1987,13 +1987,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
         <v>58</v>
@@ -2007,13 +2007,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
         <v>60</v>
@@ -2027,13 +2027,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
         <v>62</v>
@@ -2047,13 +2047,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s">
         <v>64</v>
@@ -2067,13 +2067,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B13" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D13" t="s">
         <v>75</v>
@@ -2087,13 +2087,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
         <v>77</v>
@@ -2107,13 +2107,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
         <v>81</v>
@@ -2147,13 +2147,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
         <v>87</v>
@@ -2167,13 +2167,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
         <v>89</v>
@@ -2187,13 +2187,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
         <v>91</v>
@@ -2207,13 +2207,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
         <v>93</v>
@@ -2227,13 +2227,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D21" t="s">
         <v>95</v>
@@ -2247,13 +2247,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C22" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
         <v>97</v>
@@ -2267,13 +2267,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
         <v>105</v>
@@ -2287,13 +2287,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D24" t="s">
         <v>107</v>
@@ -2307,13 +2307,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -2327,13 +2327,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
         <v>111</v>
@@ -2347,13 +2347,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B27" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
         <v>113</v>
@@ -2367,13 +2367,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
         <v>115</v>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
         <v>117</v>
@@ -2407,13 +2407,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
         <v>119</v>
@@ -2422,172 +2422,172 @@
         <v>120</v>
       </c>
       <c r="F30" t="s">
-        <v>129</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D31" t="s">
         <v>121</v>
       </c>
       <c r="E31" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F31" t="s">
-        <v>130</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E32" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F32" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E33" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="F33" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E34" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="F34" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B35" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E35" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F36" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F37" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B38" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E38" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F38" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B39" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
         <v>119</v>
@@ -2596,118 +2596,118 @@
         <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B40" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
         <v>121</v>
       </c>
       <c r="E40" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F40" t="s">
-        <v>130</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
         <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="F41" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
         <v>50</v>
       </c>
       <c r="E42" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F42" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B43" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E43" t="s">
         <v>55</v>
       </c>
       <c r="F43" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E44" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="F44" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D45" t="s">
         <v>58</v>
@@ -2721,13 +2721,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C46" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D46" t="s">
         <v>60</v>
@@ -2736,18 +2736,18 @@
         <v>61</v>
       </c>
       <c r="F46" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
         <v>62</v>
@@ -2761,13 +2761,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C48" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
         <v>64</v>
@@ -2781,16 +2781,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B49" t="s">
+        <v>138</v>
+      </c>
+      <c r="C49" t="s">
+        <v>137</v>
+      </c>
+      <c r="D49" t="s">
         <v>147</v>
-      </c>
-      <c r="C49" t="s">
-        <v>146</v>
-      </c>
-      <c r="D49" t="s">
-        <v>156</v>
       </c>
       <c r="E49" t="s">
         <v>80</v>
@@ -2801,33 +2801,33 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" t="s">
         <v>147</v>
       </c>
-      <c r="C50" t="s">
-        <v>146</v>
-      </c>
-      <c r="D50" t="s">
-        <v>156</v>
-      </c>
       <c r="E50" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F50" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C51" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D51" t="s">
         <v>81</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B52" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
         <v>105</v>
@@ -2861,13 +2861,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C53" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D53" t="s">
         <v>107</v>
@@ -2881,19 +2881,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
         <v>109</v>
       </c>
       <c r="E54" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F54" t="s">
         <v>124</v>
@@ -2901,19 +2901,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C55" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D55" t="s">
         <v>111</v>
       </c>
       <c r="E55" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="F55" t="s">
         <v>125</v>
@@ -2921,93 +2921,93 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E56" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F56" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C57" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D57" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E57" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F57" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C58" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E58" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F58" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B59" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C59" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D59" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E59" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="F59" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B60" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
         <v>115</v>
@@ -3021,13 +3021,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D61" t="s">
         <v>117</v>
@@ -3041,342 +3041,342 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B62" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E62" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="F62" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C63" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E63" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="F63" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B64" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E64" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F64" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B65" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D65" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="E65" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="F65" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B66" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D66" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E66" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F66" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D67" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E67" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="F67" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>220</v>
+      </c>
+      <c r="B68" t="s">
+        <v>138</v>
+      </c>
+      <c r="C68" t="s">
+        <v>137</v>
+      </c>
+      <c r="D68" t="s">
+        <v>172</v>
+      </c>
+      <c r="E68" t="s">
+        <v>197</v>
+      </c>
+      <c r="F68" t="s">
         <v>230</v>
-      </c>
-      <c r="B68" t="s">
-        <v>147</v>
-      </c>
-      <c r="C68" t="s">
-        <v>146</v>
-      </c>
-      <c r="D68" t="s">
-        <v>181</v>
-      </c>
-      <c r="E68" t="s">
-        <v>207</v>
-      </c>
-      <c r="F68" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B69" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D69" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E69" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F69" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C70" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D70" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E70" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F70" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B71" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C71" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D71" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="F71" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B72" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C72" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D72" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E72" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F72" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B73" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C73" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D73" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E73" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F73" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C74" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D74" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E74" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="F74" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C75" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D75" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E75" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F75" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B76" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C76" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D76" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E76" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="F76" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B77" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C77" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D77" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E77" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="F77" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C78" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D78" t="s">
         <v>48</v>
       </c>
       <c r="E78" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F78" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
